--- a/Week 3/Lab3.xlsx
+++ b/Week 3/Lab3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ngocb\Downloads\Book\Education\Cources\Physic Lab\Assignment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ngocb\Downloads\Book\Education\Cources\Physic Lab\Assignment\Week 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F05B1FAD-0E76-4FA9-93BB-EBE0B8C8AD83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97847A2B-E30A-4321-B1D7-74D588982C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{9099BA11-7AC2-49D7-B1D3-229A2D758FE5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Disk</t>
   </si>
@@ -53,24 +53,74 @@
     <t>Thickness (m)</t>
   </si>
   <si>
-    <t>Mass (m)</t>
-  </si>
-  <si>
     <t xml:space="preserve">pi </t>
   </si>
   <si>
     <t>V (m3)</t>
   </si>
   <si>
-    <t>p (g/m3)</t>
+    <t>Circumference(cm)</t>
+  </si>
+  <si>
+    <t>Diameter (mm)</t>
+  </si>
+  <si>
+    <t>Thickness (mm)</t>
+  </si>
+  <si>
+    <t>Mass (kg)</t>
+  </si>
+  <si>
+    <t>Mass (g)</t>
+  </si>
+  <si>
+    <t>==&gt;</t>
+  </si>
+  <si>
+    <t>p (kg/m3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>r^2 (mm)</t>
+  </si>
+  <si>
+    <t>r^2 (m)</t>
+  </si>
+  <si>
+    <t>Average:</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>pi</t>
+  </si>
+  <si>
+    <t>density</t>
+  </si>
+  <si>
+    <t>Direct/Tabular</t>
+  </si>
+  <si>
+    <t>Graphical</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -86,7 +136,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -94,13 +144,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -118,6 +210,1923 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>C vs. d</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$8:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4.582E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.4789999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10865</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.16500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$8:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.67</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DD52-476E-9A37-A4444AB465E9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1204487615"/>
+        <c:axId val="1075732415"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1204487615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1075732415"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1075732415"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1204487615"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>m vs. r^2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$2:$G$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5.2486809999999998E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3983860249999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9512056249999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.8062500000000007E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1024999999999998E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$E$8:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.5099999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.02E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10490000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.18769999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.32419999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E67C-41D5-8B7B-E26CDD444A11}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1251948063"/>
+        <c:axId val="1251949983"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1251948063"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1251949983"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1251949983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1251948063"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>21131</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>601916</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>164566</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B3B2DDE-B680-7869-3332-183FC70C9F6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>32018</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>155601</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>454639</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>113339</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0790579-9749-BFE2-F59D-ED963AC2580C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -437,188 +2446,435 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E41353B1-074E-450A-9641-F129949598CC}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2">
+        <f xml:space="preserve"> B8 *100</f>
+        <v>15</v>
+      </c>
+      <c r="C2" s="2">
+        <f xml:space="preserve"> C8*1000</f>
+        <v>45.82</v>
+      </c>
+      <c r="D2" s="2">
+        <f xml:space="preserve"> D8 * 1000</f>
+        <v>177.7</v>
+      </c>
+      <c r="E2" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="F2" s="2">
+        <f xml:space="preserve"> (C2/2)^2</f>
+        <v>524.86810000000003</v>
+      </c>
+      <c r="G2" s="2">
+        <f xml:space="preserve"> (C8/2)^2</f>
+        <v>5.2486809999999998E-4</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="2">
+        <f t="shared" ref="B3:B6" si="0" xml:space="preserve"> B9 *100</f>
+        <v>24</v>
+      </c>
+      <c r="C3" s="2">
+        <f t="shared" ref="C3:C6" si="1" xml:space="preserve"> C9*1000</f>
+        <v>74.789999999999992</v>
+      </c>
+      <c r="D3" s="2">
+        <f xml:space="preserve"> D9 * 1000</f>
+        <v>177.7</v>
+      </c>
+      <c r="E3" s="2">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F5" si="2" xml:space="preserve"> (C3/2)^2</f>
+        <v>1398.3860249999998</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G6" si="3" xml:space="preserve"> (C9/2)^2</f>
+        <v>1.3983860249999998E-3</v>
+      </c>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" s="2">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" si="1"/>
+        <v>108.64999999999999</v>
+      </c>
+      <c r="D4" s="2">
+        <f xml:space="preserve"> D10 * 1000</f>
+        <v>177.7</v>
+      </c>
+      <c r="E4" s="2">
+        <v>104.9</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="2"/>
+        <v>2951.2056249999996</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" si="3"/>
+        <v>2.9512056249999998E-3</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B5" s="2">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" si="1"/>
+        <v>165</v>
+      </c>
+      <c r="D5" s="2">
+        <f xml:space="preserve"> D11 * 1000</f>
+        <v>177.7</v>
+      </c>
+      <c r="E5" s="2">
+        <v>187.7</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="2"/>
+        <v>6806.25</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="3"/>
+        <v>6.8062500000000007E-3</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="J5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
+      <c r="B6" s="2">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+      <c r="D6" s="2">
+        <f xml:space="preserve"> D12 * 1000</f>
+        <v>177.7</v>
+      </c>
+      <c r="E6" s="2">
+        <v>324.2</v>
+      </c>
+      <c r="F6" s="2">
+        <f xml:space="preserve"> ROUND((C6/2)^2,2)</f>
+        <v>11025</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="3"/>
+        <v>1.1024999999999998E-2</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="J6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="3">
+        <v>3.222</v>
+      </c>
+      <c r="L6" s="3">
+        <v>53.564</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="C7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="3">
+        <v>3.0891999999999999</v>
+      </c>
+      <c r="L7" s="3">
+        <v>51.42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2">
         <v>0.15</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C8" s="2">
         <v>4.582E-2</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D8" s="2">
         <v>0.1777</v>
       </c>
-      <c r="E2" s="1">
-        <v>15.1</v>
-      </c>
-      <c r="F2">
-        <f xml:space="preserve"> B2 / C2</f>
-        <v>3.2736796158882582</v>
-      </c>
-      <c r="G2">
-        <f xml:space="preserve"> (F2*(C2^2)*D2)/4</f>
-        <v>3.0533302499999993E-4</v>
-      </c>
-      <c r="H2">
-        <f xml:space="preserve"> E2/G2</f>
-        <v>49454.198411717836</v>
+      <c r="E8" s="2">
+        <f xml:space="preserve"> E2/1000</f>
+        <v>1.5099999999999999E-2</v>
+      </c>
+      <c r="F8" s="2">
+        <f xml:space="preserve"> ROUND((B8 / C8), 2)</f>
+        <v>3.27</v>
+      </c>
+      <c r="G8" s="2">
+        <f xml:space="preserve"> ROUND(((PI()*(C8^2)*D8)/4),4)</f>
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="H8" s="2">
+        <f xml:space="preserve"> ROUND((E8/G8),2)</f>
+        <v>50.33</v>
+      </c>
+      <c r="J8" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B9" s="2">
         <v>0.24</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C9" s="2">
         <v>7.4789999999999995E-2</v>
       </c>
-      <c r="D3" s="1">
-        <v>1.7770000000000001E-2</v>
-      </c>
-      <c r="E3" s="1">
-        <v>40.200000000000003</v>
-      </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F6" si="0" xml:space="preserve"> B3 / C3</f>
-        <v>3.2089851584436424</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G6" si="1" xml:space="preserve"> (F3*(C3^2)*D3)/4</f>
-        <v>7.9741098000000009E-5</v>
-      </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H6" si="2" xml:space="preserve"> E3/G3</f>
-        <v>504131.50819668919</v>
+      <c r="D9" s="2">
+        <v>0.1777</v>
+      </c>
+      <c r="E9" s="2">
+        <f xml:space="preserve"> E3/1000</f>
+        <v>4.02E-2</v>
+      </c>
+      <c r="F9" s="2">
+        <f xml:space="preserve"> ROUND((B9 / C9), 2)</f>
+        <v>3.21</v>
+      </c>
+      <c r="G9" s="2">
+        <f xml:space="preserve"> ROUND(((PI()*(C9^2)*D9)/4),4)</f>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="H9" s="2">
+        <f xml:space="preserve"> ROUND((E9/G9),2)</f>
+        <v>50.25</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B10" s="2">
         <v>0.37</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C10" s="2">
         <v>0.10865</v>
       </c>
-      <c r="D4" s="1">
-        <v>1.7770000000000001E-2</v>
-      </c>
-      <c r="E4" s="1">
-        <v>104.9</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
-        <v>3.4054302807179018</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="1"/>
-        <v>1.7859072125E-4</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="2"/>
-        <v>587376.54042594892</v>
+      <c r="D10" s="2">
+        <v>0.1777</v>
+      </c>
+      <c r="E10" s="2">
+        <f xml:space="preserve"> E4/1000</f>
+        <v>0.10490000000000001</v>
+      </c>
+      <c r="F10" s="2">
+        <f xml:space="preserve"> ROUND((B10 / C10), 2)</f>
+        <v>3.41</v>
+      </c>
+      <c r="G10" s="2">
+        <f xml:space="preserve"> ROUND(((PI()*(C10^2)*D10)/4),4)</f>
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="H10" s="2">
+        <f xml:space="preserve"> ROUND((E10/G10),2)</f>
+        <v>65.56</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B11" s="2">
         <v>0.5</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C11" s="2">
         <v>0.16500000000000001</v>
       </c>
-      <c r="D5" s="1">
-        <v>1.7770000000000001E-2</v>
-      </c>
-      <c r="E5" s="1">
-        <v>187.7</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
-        <v>3.0303030303030303</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="1"/>
-        <v>3.6650625000000004E-4</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="2"/>
-        <v>512133.14916184911</v>
+      <c r="D11" s="2">
+        <v>0.1777</v>
+      </c>
+      <c r="E11" s="2">
+        <f xml:space="preserve"> E5/1000</f>
+        <v>0.18769999999999998</v>
+      </c>
+      <c r="F11" s="2">
+        <f xml:space="preserve"> ROUND((B11 / C11), 2)</f>
+        <v>3.03</v>
+      </c>
+      <c r="G11" s="2">
+        <f xml:space="preserve"> ROUND(((PI()*(C11^2)*D11)/4),4)</f>
+        <v>3.8E-3</v>
+      </c>
+      <c r="H11" s="2">
+        <f xml:space="preserve"> ROUND((E11/G11),2)</f>
+        <v>49.39</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B12" s="2">
         <v>0.67</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C12" s="2">
         <v>0.21</v>
       </c>
-      <c r="D6" s="1">
-        <v>1.7770000000000001E-2</v>
-      </c>
-      <c r="E6" s="1">
-        <v>324.2</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
-        <v>3.1904761904761907</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="1"/>
-        <v>6.2505975000000001E-4</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="2"/>
-        <v>518670.41510831565</v>
-      </c>
+      <c r="D12" s="2">
+        <v>0.1777</v>
+      </c>
+      <c r="E12" s="2">
+        <f xml:space="preserve"> E6/1000</f>
+        <v>0.32419999999999999</v>
+      </c>
+      <c r="F12" s="2">
+        <f xml:space="preserve"> ROUND((B12 / C12), 2)</f>
+        <v>3.19</v>
+      </c>
+      <c r="G12" s="2">
+        <f xml:space="preserve"> ROUND(((PI()*(C12^2)*D12)/4),4)</f>
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="H12" s="2">
+        <f xml:space="preserve"> ROUND((E12/G12),2)</f>
+        <v>52.29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F14" s="11">
+        <f xml:space="preserve"> (SUM(F8:F12))/5</f>
+        <v>3.222</v>
+      </c>
+      <c r="H14" s="11">
+        <f xml:space="preserve"> (SUM(H8:H12))/5</f>
+        <v>53.564</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E18" s="10"/>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E20" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Week 3/Lab3.xlsx
+++ b/Week 3/Lab3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ngocb\Downloads\Book\Education\Cources\Physic Lab\Assignment\Week 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97847A2B-E30A-4321-B1D7-74D588982C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC335E2-9C48-451D-8920-A4B5EE798C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{9099BA11-7AC2-49D7-B1D3-229A2D758FE5}"/>
   </bookViews>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D2" s="2">
         <f xml:space="preserve"> D8 * 1000</f>
-        <v>177.7</v>
+        <v>17.77</v>
       </c>
       <c r="E2" s="2">
         <v>15.1</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="D3" s="2">
         <f xml:space="preserve"> D9 * 1000</f>
-        <v>177.7</v>
+        <v>17.77</v>
       </c>
       <c r="E3" s="2">
         <v>40.200000000000003</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="D4" s="2">
         <f xml:space="preserve"> D10 * 1000</f>
-        <v>177.7</v>
+        <v>17.77</v>
       </c>
       <c r="E4" s="2">
         <v>104.9</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="D5" s="2">
         <f xml:space="preserve"> D11 * 1000</f>
-        <v>177.7</v>
+        <v>17.77</v>
       </c>
       <c r="E5" s="2">
         <v>187.7</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="D6" s="2">
         <f xml:space="preserve"> D12 * 1000</f>
-        <v>177.7</v>
+        <v>17.77</v>
       </c>
       <c r="E6" s="2">
         <v>324.2</v>
@@ -2692,7 +2692,7 @@
         <v>4.582E-2</v>
       </c>
       <c r="D8" s="2">
-        <v>0.1777</v>
+        <v>1.7770000000000001E-2</v>
       </c>
       <c r="E8" s="2">
         <f xml:space="preserve"> E2/1000</f>
@@ -2703,12 +2703,12 @@
         <v>3.27</v>
       </c>
       <c r="G8" s="2">
-        <f xml:space="preserve"> ROUND(((PI()*(C8^2)*D8)/4),4)</f>
-        <v>2.9999999999999997E-4</v>
+        <f xml:space="preserve"> ROUND(((PI()*(C8^2)*D8)/4),6)</f>
+        <v>2.9E-5</v>
       </c>
       <c r="H8" s="2">
         <f xml:space="preserve"> ROUND((E8/G8),2)</f>
-        <v>50.33</v>
+        <v>520.69000000000005</v>
       </c>
       <c r="J8" t="s">
         <v>13</v>
@@ -2725,7 +2725,7 @@
         <v>7.4789999999999995E-2</v>
       </c>
       <c r="D9" s="2">
-        <v>0.1777</v>
+        <v>1.7770000000000001E-2</v>
       </c>
       <c r="E9" s="2">
         <f xml:space="preserve"> E3/1000</f>
@@ -2736,12 +2736,12 @@
         <v>3.21</v>
       </c>
       <c r="G9" s="2">
-        <f xml:space="preserve"> ROUND(((PI()*(C9^2)*D9)/4),4)</f>
-        <v>8.0000000000000004E-4</v>
+        <f t="shared" ref="G9:G12" si="4" xml:space="preserve"> ROUND(((PI()*(C9^2)*D9)/4),6)</f>
+        <v>7.7999999999999999E-5</v>
       </c>
       <c r="H9" s="2">
         <f xml:space="preserve"> ROUND((E9/G9),2)</f>
-        <v>50.25</v>
+        <v>515.38</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -2755,7 +2755,7 @@
         <v>0.10865</v>
       </c>
       <c r="D10" s="2">
-        <v>0.1777</v>
+        <v>1.7770000000000001E-2</v>
       </c>
       <c r="E10" s="2">
         <f xml:space="preserve"> E4/1000</f>
@@ -2766,12 +2766,12 @@
         <v>3.41</v>
       </c>
       <c r="G10" s="2">
-        <f xml:space="preserve"> ROUND(((PI()*(C10^2)*D10)/4),4)</f>
-        <v>1.6000000000000001E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.65E-4</v>
       </c>
       <c r="H10" s="2">
         <f xml:space="preserve"> ROUND((E10/G10),2)</f>
-        <v>65.56</v>
+        <v>635.76</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -2785,7 +2785,7 @@
         <v>0.16500000000000001</v>
       </c>
       <c r="D11" s="2">
-        <v>0.1777</v>
+        <v>1.7770000000000001E-2</v>
       </c>
       <c r="E11" s="2">
         <f xml:space="preserve"> E5/1000</f>
@@ -2796,12 +2796,12 @@
         <v>3.03</v>
       </c>
       <c r="G11" s="2">
-        <f xml:space="preserve"> ROUND(((PI()*(C11^2)*D11)/4),4)</f>
-        <v>3.8E-3</v>
+        <f t="shared" si="4"/>
+        <v>3.8000000000000002E-4</v>
       </c>
       <c r="H11" s="2">
         <f xml:space="preserve"> ROUND((E11/G11),2)</f>
-        <v>49.39</v>
+        <v>493.95</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -2815,7 +2815,7 @@
         <v>0.21</v>
       </c>
       <c r="D12" s="2">
-        <v>0.1777</v>
+        <v>1.7770000000000001E-2</v>
       </c>
       <c r="E12" s="2">
         <f xml:space="preserve"> E6/1000</f>
@@ -2826,12 +2826,12 @@
         <v>3.19</v>
       </c>
       <c r="G12" s="2">
-        <f xml:space="preserve"> ROUND(((PI()*(C12^2)*D12)/4),4)</f>
-        <v>6.1999999999999998E-3</v>
+        <f t="shared" si="4"/>
+        <v>6.1499999999999999E-4</v>
       </c>
       <c r="H12" s="2">
         <f xml:space="preserve"> ROUND((E12/G12),2)</f>
-        <v>52.29</v>
+        <v>527.15</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="H14" s="11">
         <f xml:space="preserve"> (SUM(H8:H12))/5</f>
-        <v>53.564</v>
+        <v>538.58600000000001</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
